--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488283_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488283_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4504</v>
+        <v>11.9948</v>
       </c>
       <c r="E2" t="n">
-        <v>10.4976</v>
+        <v>11.042</v>
       </c>
       <c r="F2" t="n">
         <v>0.9528</v>
@@ -610,10 +610,10 @@
         <v>1.297</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4514</v>
+        <v>0.0929</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7449</v>
+        <v>-0.2005</v>
       </c>
       <c r="U2" t="n">
         <v>0.2934</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3515</v>
+        <v>4.6709</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2467</v>
+        <v>4.7139</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1047</v>
+        <v>-0.043</v>
       </c>
       <c r="G3" t="n">
         <v>7.0568</v>
@@ -688,13 +688,13 @@
         <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5181</v>
+        <v>0.8375</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.2469</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.5907</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6294</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8943</v>
+        <v>3.1881</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9398</v>
+        <v>2.2336</v>
       </c>
       <c r="F4" t="n">
         <v>0.9545</v>
@@ -766,10 +766,10 @@
         <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4974</v>
+        <v>-0.2036</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3071</v>
+        <v>-0.0134</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1903</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8377</v>
+        <v>1.6387</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3683</v>
+        <v>1.8616</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5306</v>
+        <v>-0.223</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3191</v>
+        <v>3.0551</v>
       </c>
       <c r="H5" t="n">
-        <v>1.286</v>
+        <v>0.7098</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6051</v>
+        <v>2.3454</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4603</v>
+        <v>3.6028</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5587</v>
+        <v>1.5802</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0984</v>
+        <v>2.0227</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7794</v>
+        <v>-0.5477</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2727</v>
+        <v>-0.8704</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5067</v>
+        <v>0.3227</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7411</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R5" t="n">
         <v>0.7411</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7857</v>
+        <v>-0.3227</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6491</v>
+        <v>-0.2207</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1365</v>
+        <v>-0.102</v>
       </c>
       <c r="V5" t="n">
-        <v>0.63</v>
+        <v>0.9444</v>
       </c>
       <c r="W5" t="n">
         <v>1.2589</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2896</v>
+        <v>1.4033</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6111</v>
+        <v>1.8355</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3214</v>
+        <v>-0.4321</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0551</v>
+        <v>-0.3191</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7098</v>
+        <v>1.286</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3454</v>
+        <v>-1.6051</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6028</v>
+        <v>0.4603</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5802</v>
+        <v>1.5587</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0227</v>
+        <v>-1.0984</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5477</v>
+        <v>-0.7794</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8704</v>
+        <v>-0.2727</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3227</v>
+        <v>-0.5067</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0382</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6718</v>
+        <v>0.3513</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4713</v>
+        <v>0.1163</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2005</v>
+        <v>0.235</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9444</v>
+        <v>0.63</v>
       </c>
       <c r="W6" t="n">
         <v>1.2589</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALVERDE PIZARRO</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5797</v>
+        <v>0.3649</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0191</v>
+        <v>0.0107</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5605</v>
+        <v>0.3542</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8471</v>
+        <v>2.5582</v>
       </c>
       <c r="H8" t="n">
-        <v>0.354</v>
+        <v>-0.0684</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4931</v>
+        <v>2.6266</v>
       </c>
       <c r="J8" t="n">
-        <v>1.198</v>
+        <v>2.8245</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0736</v>
+        <v>0.1288</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1244</v>
+        <v>2.6956</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3508</v>
+        <v>-0.2663</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7196</v>
+        <v>-0.1973</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3687</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1117</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5292</v>
+        <v>0.0301</v>
       </c>
       <c r="T8" t="n">
-        <v>0.674</v>
+        <v>-0.0345</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1448</v>
+        <v>0.0646</v>
       </c>
       <c r="V8" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>J. VALVERDE PIZARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1204</v>
+        <v>0.2618</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2831</v>
+        <v>-0.3726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4035</v>
+        <v>0.6344</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5582</v>
+        <v>0.8471</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0684</v>
+        <v>0.354</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6266</v>
+        <v>0.4931</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8245</v>
+        <v>1.198</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1288</v>
+        <v>1.0736</v>
       </c>
       <c r="L9" t="n">
-        <v>2.6956</v>
+        <v>0.1244</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2663</v>
+        <v>-0.3508</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1973</v>
+        <v>-0.7196</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.3687</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2234</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2144</v>
+        <v>0.2114</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3283</v>
+        <v>0.2823</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1139</v>
+        <v>-0.0709</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.607</v>
+        <v>-0.7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.068</v>
+        <v>0.1227</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.675</v>
+        <v>-0.8228</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5774</v>
@@ -1234,13 +1234,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0445</v>
+        <v>-0.0485</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0124</v>
+        <v>0.0423</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0569</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.63</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4974</v>
+        <v>-2.3994</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8671</v>
+        <v>-2.7692</v>
       </c>
       <c r="F11" t="n">
         <v>0.3697</v>
@@ -1312,10 +1312,10 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1007</v>
+        <v>0.1986</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1219</v>
+        <v>-0.0239</v>
       </c>
       <c r="U11" t="n">
         <v>0.2226</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8848</v>
+        <v>-2.615</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1515</v>
+        <v>-0.9556</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7333</v>
+        <v>-1.6594</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5307</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4096</v>
+        <v>-0.1399</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1977</v>
+        <v>-0.0019</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2119</v>
+        <v>-0.138</v>
       </c>
       <c r="V12" t="n">
         <v>0.3144</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.4785</v>
+        <v>18.7522</v>
       </c>
       <c r="E13" t="n">
-        <v>18.393</v>
+        <v>18.6667</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08539999999999948</v>
+        <v>0.08529999999999993</v>
       </c>
       <c r="G13" t="n">
         <v>17.8986</v>
@@ -1456,7 +1456,7 @@
         <v>-5.5704</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.03719999999999999</v>
+        <v>-0.03720000000000005</v>
       </c>
       <c r="P13" t="n">
         <v>-8.337899999999999</v>
@@ -1468,13 +1468,13 @@
         <v>8.3377</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7336</v>
+        <v>1.0071</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.08079999999999994</v>
+        <v>0.1929</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8142</v>
+        <v>0.8143</v>
       </c>
       <c r="V13" t="n">
         <v>8.184200000000001</v>
@@ -1483,7 +1483,7 @@
         <v>11.6437</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.459499999999999</v>
+        <v>-3.4595</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8254</v>
+        <v>5.5706</v>
       </c>
       <c r="E14" t="n">
-        <v>8.5573</v>
+        <v>8.3614</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7319</v>
+        <v>-2.7909</v>
       </c>
       <c r="G14" t="n">
         <v>5.7061</v>
@@ -1546,13 +1546,13 @@
         <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1383</v>
+        <v>0.8835</v>
       </c>
       <c r="T14" t="n">
-        <v>0.582</v>
+        <v>0.3861</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5563</v>
+        <v>0.4974</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5749</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. RUEDA MURIEL</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3011</v>
+        <v>0.3986</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.4704</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8933</v>
+        <v>-0.0718</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5342</v>
+        <v>-1.844</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4635</v>
+        <v>-1.4937</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0706</v>
+        <v>-0.3502</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7601</v>
+        <v>1.4301</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0.0295</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3271</v>
+        <v>1.4006</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2943</v>
+        <v>-3.2741</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8966</v>
+        <v>-1.5233</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3977</v>
+        <v>-1.7508</v>
       </c>
       <c r="P15" t="n">
-        <v>1.297</v>
+        <v>2.2234</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R15" t="n">
-        <v>1.297</v>
+        <v>3.3352</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0639</v>
+        <v>-0.2953</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1679</v>
+        <v>-0.4769</v>
       </c>
       <c r="U15" t="n">
-        <v>0.104</v>
+        <v>0.1815</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>M. RUEDA MURIEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6364</v>
+        <v>-0.3251</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0828</v>
+        <v>0.4943</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.7192</v>
+        <v>-0.8194</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.6372</v>
+        <v>-1.5342</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.1042</v>
+        <v>-1.4635</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.533</v>
+        <v>-0.0706</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3739</v>
+        <v>0.7601</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0255</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3484</v>
+        <v>1.3271</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.0111</v>
+        <v>-2.2943</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1297</v>
+        <v>-0.8966</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8814</v>
+        <v>-1.3977</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7793</v>
+        <v>1.297</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7793</v>
+        <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1098</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.45</v>
+        <v>-0.2658</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3402</v>
+        <v>0.1778</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8883</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.1471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8172</v>
+        <v>-1.6718</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5089</v>
+        <v>2.6139</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3084</v>
+        <v>-4.2857</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.844</v>
+        <v>-2.6372</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4937</v>
+        <v>-2.1042</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3502</v>
+        <v>-0.533</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4301</v>
+        <v>1.3739</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0295</v>
+        <v>0.0255</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4006</v>
+        <v>1.3484</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.2741</v>
+        <v>-4.0111</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5233</v>
+        <v>-2.1297</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7508</v>
+        <v>-1.8814</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2234</v>
+        <v>2.7793</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3352</v>
+        <v>2.7793</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5111</v>
+        <v>0.0743</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4562</v>
+        <v>-0.0189</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.055</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3144</v>
+        <v>-1.8883</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6289</v>
+        <v>1.2589</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3144</v>
+        <v>-3.1471</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.3214</v>
+        <v>-3.2917</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5369</v>
+        <v>-3.0707</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7844</v>
+        <v>-0.2211</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8312</v>
+        <v>-2.6311</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4688</v>
+        <v>-1.7955</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3624</v>
+        <v>-0.8356</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1914</v>
+        <v>-0.0237</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0255</v>
+        <v>-0.0866</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1659</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0225</v>
+        <v>-2.6074</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4943</v>
+        <v>-1.709</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5283</v>
+        <v>-0.8984</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1853</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>-2.9646</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6676</v>
+        <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3049</v>
+        <v>0.0805</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8754</v>
+        <v>-0.0824</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5705</v>
+        <v>0.1629</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6113</v>
+        <v>-3.4215</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1686</v>
+        <v>-2.2431</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4427</v>
+        <v>-1.1784</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6311</v>
+        <v>-2.8312</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7955</v>
+        <v>-1.4688</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8356</v>
+        <v>-1.3624</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0237</v>
+        <v>0.1914</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0866</v>
+        <v>0.0255</v>
       </c>
       <c r="L19" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.1659</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6074</v>
+        <v>-3.0225</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.709</v>
+        <v>-1.4943</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8984</v>
+        <v>-1.5283</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9646</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2234</v>
+        <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.239</v>
+        <v>-0.4051</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1803</v>
+        <v>-0.5816</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0587</v>
+        <v>0.1766</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7786</v>
+        <v>-4.0557</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.61</v>
+        <v>-1.1976</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1686</v>
+        <v>-2.8582</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0435</v>
@@ -2014,13 +2014,13 @@
         <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7827</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9986</v>
+        <v>0.411</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2159</v>
+        <v>0.0945</v>
       </c>
       <c r="V20" t="n">
         <v>-2.5177</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1806</v>
+        <v>-4.7144</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5092</v>
+        <v>-1.2154</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6713</v>
+        <v>-3.499</v>
       </c>
       <c r="G21" t="n">
         <v>-4.9258</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8488</v>
+        <v>-0.3827</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4414</v>
+        <v>-0.1476</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4074</v>
+        <v>-0.235</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6575</v>
+        <v>-5.6616</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9841</v>
+        <v>-4.2986</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6734</v>
+        <v>-1.363</v>
       </c>
       <c r="G22" t="n">
         <v>-5.1579</v>
@@ -2170,13 +2170,13 @@
         <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7966</v>
+        <v>0.1993</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7237</v>
+        <v>-0.0382</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.07290000000000001</v>
+        <v>0.2375</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.4787</v>
+        <v>-17.1726</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.08540000000000081</v>
+        <v>-0.0854000000000017</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.3932</v>
+        <v>-17.0875</v>
       </c>
       <c r="G23" t="n">
         <v>-17.8988</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.6871</v>
+        <v>-5.687100000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-12.2114</v>
@@ -2248,13 +2248,13 @@
         <v>16.6759</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7335000000000003</v>
+        <v>0.572</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8142999999999998</v>
+        <v>-0.8143</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08070000000000006</v>
+        <v>1.3865</v>
       </c>
       <c r="V23" t="n">
         <v>-8.1843</v>
